--- a/decks/bomme-studio/keyword-research.xlsx
+++ b/decks/bomme-studio/keyword-research.xlsx
@@ -71,12 +71,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -600,12 +600,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wholesale Leggings: What to Expect From a Real Partner</t>
+          <t>Custom Sportswear Suppliers: What to Expect From a Real Partner</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wholesale leggings</t>
+          <t>custom sportswear suppliers</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -638,12 +638,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wholesale Activewear: The Questions to Ask on the First Call</t>
+          <t>Activewear Manufacturer: The Full-Package Guide for Scaling Brands</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wholesale activewear</t>
+          <t>activewear manufacturer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>22</v>
+        <v>390</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -676,12 +676,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wholesale Athletic Apparel: A Production-Partner Checklist</t>
+          <t>Activewear Manufacturers in the USA: A Domestic Sourcing Guide</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wholesale athletic apparel</t>
+          <t>activewear manufacturers usa</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>590</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>35</v>
+        <v>170</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -714,12 +714,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wholesale Workout Clothes: A No-Nonsense Vendor Guide</t>
+          <t>Swimsuit Companies: From Tech Pack to Finished Garment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wholesale workout clothes</t>
+          <t>swimsuit companies</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -752,12 +752,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Founder's Guide to Workout Clothes Wholesale</t>
+          <t>Custom Sportswear Manufacturer: A No-Nonsense Vendor Guide</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>workout clothes wholesale</t>
+          <t>custom sportswear manufacturer</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>30</v>
+        <v>390</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -790,12 +790,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Workout Pants for Women: The Trade-offs No One Mentions</t>
+          <t>The Founder's Guide to Sportswear Manufacturing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>workout pants for women</t>
+          <t>sportswear manufacturing</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2900</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>25</v>
+        <v>320</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -828,12 +828,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yoga Pants vs Leggings: How to Compare Your Options</t>
+          <t>Womens Workout Pants: The Real Numbers Behind the Quote</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yoga pants vs leggings</t>
+          <t>womens workout pants</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -848,14 +848,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1300</v>
+        <v>1900</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -866,12 +866,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fitness Wear Ladies: Domestic vs Overseas, Weighed Honestly</t>
+          <t>Italian Athletic Clothing Brands: The Fundamentals, Minus the Jargon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitness wear ladies</t>
+          <t>italian athletic clothing brands</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8100</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>72</v>
+        <v>3600</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -904,12 +904,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shirts Sportswear: What to Ask Before You Commit</t>
+          <t>Best USA Activewear Manufacturers for Established Brands</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>shirts sportswear</t>
+          <t>best activewear manufacturers</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>42</v>
+        <v>170</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -942,12 +942,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Comfortable Activewear: Domestic vs Overseas, Weighed Honestly</t>
+          <t>Fitness Wear Ladies: Domestic vs Overseas, Weighed Honestly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>comfortable activewear</t>
+          <t>fitness wear ladies</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>65</v>
+        <v>8100</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -980,12 +980,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sportswear List: The Fundamentals, Minus the Jargon</t>
+          <t>Shirts Sportswear: What to Ask Before You Commit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sportswear list</t>
+          <t>shirts sportswear</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -995,19 +995,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8100</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>44</v>
+        <v>3600</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sportswear Brands: A Quick, Honest Overview</t>
+          <t>Comfortable Activewear: Domestic vs Overseas, Weighed Honestly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sportswear brands</t>
+          <t>comfortable activewear</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1033,19 +1033,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>4400</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>50</v>
+        <v>3600</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -1056,34 +1056,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Corporate Gift Supplier: What to Expect From a Premium Partner</t>
+          <t>Activewear Apparel Brands: A Clear Explainer for Founders</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>corporate gift supplier</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Custom Merch</t>
+          <t>activewear apparel brands</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Activewear</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>590</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>29</v>
+        <v>9900</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Corporate Gift Companies: A Buyer's Checklist for Brand Teams</t>
+          <t>Yoga Wear: A Quick, Honest Overview</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>corporate gift companies</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Custom Merch</t>
+          <t>yoga wear</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Activewear</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>27</v>
+        <v>2900</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Promotional Products Suppliers: For Corporate and Hospitality Programs</t>
+          <t>Corporate Gift Supplier: What to Expect From a Premium Partner</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>promotional products suppliers</t>
+          <t>corporate gift supplier</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>77</v>
+        <v>590</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Custom Company Apparel: A Sourcing Guide for Premium Programs</t>
+          <t>Company Swag: A Guide for Brands With Real Budgets</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>custom company apparel</t>
+          <t>company swag</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>880</v>
+        <v>2400</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Swag Companies: A Practical Guide for Marketing Leads</t>
+          <t>Company Merch: How to Run a Program That Scales</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>swag companies</t>
+          <t>company merch</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>480</v>
+        <v>880</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wholesale Screen Printing: How to Run a Program That Scales</t>
+          <t>Merchandise Maker: A Buyer's Checklist for Brand Teams</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wholesale screen printing</t>
+          <t>merchandise maker</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>390</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>40</v>
+        <v>590</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Custom Merch Maker: What to Expect From a Premium Partner</t>
+          <t>Screen Printing Companies: For Corporate and Hospitality Programs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>custom merch maker</t>
+          <t>screen printing companies</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>38</v>
+        <v>480</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="22">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Custom Embroidered Sweatshirts: Premium vs Cheap, Weighed Honestly</t>
+          <t>Company Branded Clothing: From Concept to Delivered Boxes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>custom embroidered sweatshirts</t>
+          <t>company branded clothing</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>19</v>
+        <v>260</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Corporate Gifts for Clients: Cost, Minimums, and Lead Times</t>
+          <t>Branded Hoodies: What It Really Costs in 2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>corporate gifts for clients</t>
+          <t>branded hoodies</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1387,7 +1387,7 @@
         <v>1300</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Corporate Gifts Ideas: What You Should Know First</t>
+          <t>Cool Swag Ideas: Ideas That Actually Land</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>corporate gifts ideas</t>
+          <t>cool swag ideas</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>720</v>
+        <v>320</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Custom Merchandise: How to Choose the Right Partner</t>
+          <t>Custom Merchandise: Cost, Minimums, and Lead Times</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1462,7 +1462,7 @@
       <c r="G25" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="5" t="n">
         <v>61</v>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Custom Merch: What to Ask Before You Commit</t>
+          <t>Branded Apparel: Premium vs Cheap, Weighed Honestly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>custom merch</t>
+          <t>branded apparel</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2900</v>
+        <v>1600</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
@@ -1512,22 +1512,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Custom Embroidered Jumpers: A 2026 Buyer's Guide</t>
+          <t>Wholesale Sweatshirts: How to Vet One for Quality and Scale</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>custom embroidered jumpers</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Custom Merch</t>
+          <t>wholesale sweatshirts</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Premium Basics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>36</v>
+        <v>2900</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wholesale Sweatshirts: How to Vet One for Quality and Scale</t>
+          <t>Clothing Manufacturers Suppliers: A Guide for Established Brands</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wholesale sweatshirts</t>
+          <t>clothing manufacturers suppliers</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2900</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>23</v>
+        <v>8100</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="29">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Clothing Manufacturers: From Tech Pack to Delivery</t>
+          <t>Custom Hoodie Maker: The Process, Start to Finish</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>clothing manufacturers</t>
+          <t>custom hoodie maker</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>30</v>
+        <v>2900</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wholesale Hoodies: A Sourcing Guide for Growing Brands</t>
+          <t>How to Choose a Body Care Manufacturer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>wholesale hoodies</t>
+          <t>body care manufacturers</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>35</v>
+        <v>1900</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="31">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel Wholesale: A Guide for Established Brands</t>
+          <t>American Garment Brand: How to Vet One for Quality and Scale</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>los angeles apparel wholesale</t>
+          <t>american garment brand</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Custom Clothes Maker: What to Expect From a Full-Package Partner</t>
+          <t>Apparel Manufacturer in USA: A Sourcing Guide for Growing Brands</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>custom clothes maker</t>
+          <t>apparel manufacturer in usa</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>47</v>
+        <v>1600</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sweatshirt Maker: The Process, Start to Finish</t>
+          <t>Plain Black Hoodie: Cost, Lead Times, and MOQs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sweatshirt maker</t>
+          <t>plain black hoodie</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1755,19 +1755,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1600</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>43</v>
+        <v>3600</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="34">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Oversized Streetwear Hoodie: Cost, Lead Times, and MOQs</t>
+          <t>How to Dye Garments: A Founder's Primer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>oversized streetwear hoodie</t>
+          <t>how to dye garments</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1793,19 +1793,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>How to Dye Garments: What Every Brand Owner Should Know</t>
+          <t>Best Full-Package Clothing Manufacturers in the USA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>how to dye garments</t>
+          <t>best clothing manufacturers usa</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1831,19 +1831,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>10</v>
+        <v>480</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Custom Tshirt: Full-Package vs Cut-and-Sew, Weighed</t>
+          <t>Domestic vs Overseas Apparel Manufacturing: The Real Trade-offs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>custom tshirt</t>
+          <t>domestic vs overseas clothing manufacturing</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>14800</v>
+        <v>140</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Organic Cotton Clothing: What to Ask Before You Commit</t>
+          <t>Custom Hoodies: Full-Package vs Cut-and-Sew, Weighed</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>organic cotton clothing</t>
+          <t>custom hoodies</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>12100</v>
+        <v>22200</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Performance Sports Clothing: What It Really Costs in 2026</t>
+          <t>Custom Apparel: The Trade-offs No One Mentions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>performance sports clothing</t>
+          <t>custom apparel</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>52</v>
+        <v>12100</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="39">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Clothing Design: The Trade-offs No One Mentions</t>
+          <t>Sustainable Clothing: Where Most Brands Get It Wrong</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>clothing design</t>
+          <t>sustainable clothing</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>42</v>
+        <v>8100</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="40">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sustainable Clothing Brands: A Clear Explainer for Founders</t>
+          <t>Garments Brands: A Clear Explainer for Founders</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sustainable clothing brands</t>
+          <t>garments brands</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2032,8 +2032,8 @@
       <c r="G40" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="H40" s="6" t="n">
-        <v>69</v>
+      <c r="H40" s="5" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="41">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Made Clothing: The Fundamentals, Minus the Jargon</t>
+          <t>Blank T Shirt: Explained in Plain English</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>american made clothing</t>
+          <t>blank t shirt</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2068,9 +2068,9 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H41" s="5" t="n">
+        <v>4400</v>
+      </c>
+      <c r="H41" s="6" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Custom Sportswear Suppliers: Choosing a Partner You Can Scale With</t>
+          <t>Wholesale Swimwear: Choosing a Partner You Can Scale With</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>custom sportswear suppliers</t>
+          <t>wholesale swimwear</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>How to Choose a Gym Clothing Manufacturer</t>
+          <t>Custom Activewear Manufacturer: What Performance Brands Should Look For</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>gym clothing manufacturers</t>
+          <t>custom activewear manufacturer</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2184,8 +2184,8 @@
       <c r="G44" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="H44" s="4" t="n">
-        <v>25</v>
+      <c r="H44" s="6" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Swimsuit Companies: From Tech Pack to Finished Garment</t>
+          <t>Sportswear Manufacturer: A Sourcing Guide for Scaling Activewear Brands</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>swimsuit companies</t>
+          <t>sportswear manufacturer</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Custom Sportswear Manufacturer: What Separates Real Partners From Brokers</t>
+          <t>Sportswear Companies: Inside the Process, Start to Finish</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>custom sportswear manufacturer</t>
+          <t>sportswear companies</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>390</v>
+        <v>590</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sportswear Manufacturing: A Sourcing Guide for Scaling Activewear Brands</t>
+          <t>American Made Swimsuits: What Separates Real Partners From Brokers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sportswear manufacturing</t>
+          <t>american made swimsuits</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>33</v>
+        <v>480</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Womens Workout Pants: The Real Numbers Behind the Quote</t>
+          <t>American Made Swimwear: A Sourcing Guide for Scaling Activewear Brands</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>womens workout pants</t>
+          <t>american made swimwear</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2325,19 +2325,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>24</v>
+        <v>390</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="49">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Italian Athletic Clothing Brands: What Every Athletic Brand Should Know</t>
+          <t>Swimwear Fabric Material: Where Most Brands Get It Wrong</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>italian athletic clothing brands</t>
+          <t>swimwear fabric material</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2363,19 +2363,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>3600</v>
+        <v>1900</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Activewear for Ladies: Cost, Lead Times, and MOQs</t>
+          <t>Italian Sportswear Brand: Explained in Plain English</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>activewear for ladies</t>
+          <t>italian sportswear brand</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2401,19 +2401,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>8100</v>
-      </c>
-      <c r="H50" s="6" t="n">
-        <v>69</v>
+        <v>1600</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Athletic Performance Apparel: What It Really Costs in 2026</t>
+          <t>Activewear for Ladies: Cost, Lead Times, and MOQs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>athletic performance apparel</t>
+          <t>activewear for ladies</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>82</v>
+        <v>8100</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="52">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gym Clothes Apparel: A 2026 Buyer's Guide</t>
+          <t>Athletic Performance Apparel: What It Really Costs in 2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>gym clothes apparel</t>
+          <t>athletic performance apparel</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>4400</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>76</v>
+        <v>6600</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="53">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fitness Apparel Clothing: What It Really Costs in 2026</t>
+          <t>Gym Clothes Apparel: A 2026 Buyer's Guide</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>fitness apparel clothing</t>
+          <t>gym clothes apparel</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>74</v>
+        <v>4400</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="54">
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Types of Workouts: A Founder's Primer</t>
+          <t>Fitness Apparel Clothing: What It Really Costs in 2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>types of workouts</t>
+          <t>fitness apparel clothing</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2553,19 +2553,19 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>5400</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>57</v>
+        <v>3600</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="55">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Yoga Wear: The Short Version for Busy Founders</t>
+          <t>Types of Workouts: What Every Athletic Brand Should Know</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>yoga wear</t>
+          <t>types of workouts</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>2900</v>
+        <v>5400</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56">
@@ -2614,34 +2614,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Swag for Companies: Built for Budgets That Mean Business</t>
+          <t>Running Apparel: What You Should Know First</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>swag for companies</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Custom Merch</t>
+          <t>running apparel</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Activewear</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>15</v>
+        <v>2900</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="57">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Company Apparel: What Established Brands Expect</t>
+          <t>Swag for Companies: Built for Budgets That Mean Business</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>company apparel</t>
+          <t>swag for companies</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>880</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>44</v>
+        <v>320</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Company Merchandise: From Concept to Delivered Boxes</t>
+          <t>Promotional Products Suppliers: For Corporate and Hospitality Programs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>company merchandise</t>
+          <t>promotional products suppliers</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2714,9 +2714,9 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H58" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H58" s="5" t="n">
         <v>77</v>
       </c>
     </row>
@@ -2728,12 +2728,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Embroidery Company: A Guide for Brands With Real Budgets</t>
+          <t>Custom Company Apparel: A Sourcing Guide for Premium Programs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>embroidery company</t>
+          <t>custom company apparel</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>590</v>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>62</v>
+        <v>880</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="60">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Company Branded Apparel: A Sourcing Guide for Premium Programs</t>
+          <t>Swag Companies: A Practical Guide for Marketing Leads</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>company branded apparel</t>
+          <t>swag companies</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>43</v>
+        <v>480</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="61">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Embroidery Pullover Sweatshirt: How to Choose the Right Partner</t>
+          <t>Wholesale Screen Printing: How to Run a Program That Scales</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>embroidery pullover sweatshirt</t>
+          <t>wholesale screen printing</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>20</v>
+        <v>390</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="62">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Embroidery Logo: How to Compare Your Options</t>
+          <t>Corporate Gifts for Clients: Cost, Minimums, and Lead Times</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>embroidery logo</t>
+          <t>corporate gifts for clients</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Swag Ideas: What Every Marketing Lead Should Know</t>
+          <t>Service Merch: The Trade-offs No One Mentions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>swag ideas</t>
+          <t>service merch</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DTG Printing: Premium vs Cheap, Weighed Honestly</t>
+          <t>Swag Ideas: A Brand's Guide to Getting It Right</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dtg printing</t>
+          <t>swag ideas</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H64" s="6" t="n">
-        <v>59</v>
+        <v>720</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="65">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Screen Printing Silk Screening: Cost, Minimums, and Lead Times</t>
+          <t>Business Swag Ideas: A Brand's Guide to Getting It Right</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>screen printing silk screening</t>
+          <t>business swag ideas</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>45</v>
+        <v>210</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Custom Screen Printing: The Real Numbers Behind the Quote</t>
+          <t>Best Custom Merch Companies for Corporate and Hospitality Programs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>custom screen printing</t>
+          <t>best custom merch companies</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>33</v>
+        <v>320</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="67">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Merchandise: A Brand's Guide to Getting It Right</t>
+          <t>DTG Printing: Cost, Minimums, and Lead Times</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>merchandise</t>
+          <t>dtg printing</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3047,19 +3047,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>22200</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>69</v>
+        <v>6600</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="68">
@@ -3070,34 +3070,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mercht: What Every Marketing Lead Should Know</t>
+          <t>LA Apparel Wholesale: Choosing a Partner You Can Grow With</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>mercht</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Custom Merch</t>
+          <t>la apparel wholesale</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Premium Basics</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>33</v>
+        <v>1900</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="69">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LA Apparel Wholesale: Choosing a Partner You Can Grow With</t>
+          <t>Clothing Manufacturers: From Tech Pack to Delivery</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>la apparel wholesale</t>
+          <t>clothing manufacturers</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v>27</v>
+        <v>6600</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="70">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hoodie Maker: What to Expect From a Full-Package Partner</t>
+          <t>Wholesale Hoodies: A Sourcing Guide for Growing Brands</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>hoodie maker</t>
+          <t>wholesale hoodies</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>4400</v>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>34</v>
+        <v>2400</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="71">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wholesale Clothing Sweatshirts: What Funded Brands Should Look For</t>
+          <t>Los Angeles Apparel Wholesale: A Guide for Established Brands</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>wholesale clothing sweatshirts</t>
+          <t>los angeles apparel wholesale</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>35</v>
+        <v>1600</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="72">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hoodie in Wholesale: From Tech Pack to Delivery</t>
+          <t>What to Look For in a Custom Clothes Maker</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>hoodie in wholesale</t>
+          <t>custom clothes maker</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>1600</v>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>30</v>
+        <v>1900</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="73">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Garment Manufacturers: How to Vet One for Quality and Scale</t>
+          <t>Sweatshirt Maker: A Production-Partner Checklist</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>american garment manufacturers</t>
+          <t>sweatshirt maker</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -3286,8 +3286,8 @@
       <c r="G73" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="H73" s="5" t="n">
-        <v>35</v>
+      <c r="H73" s="6" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="74">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Clothing Manufacturers in USA: A Sourcing Guide for Growing Brands</t>
+          <t>Blank Hoodies: A Side-by-Side Breakdown</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>clothing manufacturers in usa</t>
+          <t>blank hoodies</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>1600</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>48</v>
+        <v>8100</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="75">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blank Hoodies: The Real Numbers Behind the Quote</t>
+          <t>How to Choose a Clothing Manufacturer: A Founder's Checklist</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>blank hoodies</t>
+          <t>how to choose a clothing manufacturer</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
@@ -3356,14 +3356,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>8100</v>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="76">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Plain Black Hoodie: Full-Package vs Cut-and-Sew, Weighed</t>
+          <t>Custom Sweatshirts: A Side-by-Side Breakdown</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>plain black hoodie</t>
+          <t>custom sweatshirts</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -3394,14 +3394,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>29</v>
+        <v>12100</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="77">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Custom Hoodies: Full-Package vs Cut-and-Sew, Weighed</t>
+          <t>Organic Cotton Clothing: The Real Numbers Behind the Quote</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>custom hoodies</t>
+          <t>organic cotton clothing</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>22200</v>
+        <v>12100</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Streetwear Hoodies: The Trade-offs No One Mentions</t>
+          <t>Clothing Brands: What Every Brand Owner Should Know</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>streetwear hoodies</t>
+          <t>clothing brands</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -3465,19 +3465,19 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>9900</v>
+        <v>27100</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Black Tee: Where Most Brands Get It Wrong</t>
+          <t>Tee Shirts, Explained</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>black tee</t>
+          <t>tee shirts</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -3503,19 +3503,19 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>5400</v>
+        <v>12100</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Brand Owner's Guide to Tee Shirts</t>
+          <t>Sustainable Clothing Brands: The Fundamentals, Minus the Jargon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>tee shirts</t>
+          <t>sustainable clothing brands</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>12100</v>
-      </c>
-      <c r="H80" s="6" t="n">
-        <v>60</v>
+        <v>9900</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="81">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Blank T Shirt: A Founder's Primer</t>
+          <t>Sustainable Garments: A Quick, Honest Overview</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>blank t shirt</t>
+          <t>sustainable garments</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>4400</v>
+        <v>5400</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wholesale Clothing Swimwear: A Buyer's Guide for Growing Athletic Brands</t>
+          <t>Wholesale Leggings: A Buyer's Guide for Growing Athletic Brands</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>wholesale clothing swimwear</t>
+          <t>wholesale leggings</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wholesale Swimwear: Inside the Process, Start to Finish</t>
+          <t>Wholesale Activewear: Scaling From First Run to Reorder</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>wholesale swimwear</t>
+          <t>wholesale activewear</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sportswear Manufacturer: A Sourcing Guide for Scaling Activewear Brands</t>
+          <t>Private Label Activewear: How to Launch Without Building a Factory</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>sportswear manufacturer</t>
+          <t>private label activewear</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>880</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>44</v>
+        <v>210</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="85">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sportswear Companies: A Guide for Funded Performance Brands</t>
+          <t>Wholesale Athletic Apparel: A Production-Partner Checklist</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>sportswear companies</t>
+          <t>wholesale athletic apparel</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
         <v>590</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American Made Swimsuits: Scaling From First Run to Reorder</t>
+          <t>Wholesale Workout Clothes: A Guide for Funded Performance Brands</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>american made swimsuits</t>
+          <t>wholesale workout clothes</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3780,8 +3780,8 @@
       <c r="G86" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="H86" s="5" t="n">
-        <v>49</v>
+      <c r="H86" s="6" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="87">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>American Made Swimwear: What Performance Brands Should Look For</t>
+          <t>Workout Clothes Wholesale: The Questions to Ask on the First Call</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>american made swimwear</t>
+          <t>workout clothes wholesale</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Swimwear Fabric Material: Where Most Brands Get It Wrong</t>
+          <t>Workout Pants for Women: The Trade-offs No One Mentions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>swimwear fabric material</t>
+          <t>workout pants for women</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>1900</v>
+        <v>2900</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Italian Sportswear Brand: What You Should Know First</t>
+          <t>Yoga Pants vs Leggings: How to Compare Your Options</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>italian sportswear brand</t>
+          <t>yoga pants vs leggings</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3883,19 +3883,19 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Workout Clothes for Women: How to Compare Your Options</t>
+          <t>The Brand Owner's Guide to Sportswear Types</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>workout clothes for women</t>
+          <t>sportswear types</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3921,19 +3921,19 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>9900</v>
-      </c>
-      <c r="H90" s="6" t="n">
-        <v>62</v>
+        <v>1300</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="91">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Womens Workout Clothes: How to Choose the Right Partner</t>
+          <t>Workout Clothes for Women: How to Compare Your Options</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>womens workout clothes</t>
+          <t>workout clothes for women</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>4400</v>
-      </c>
-      <c r="H91" s="6" t="n">
-        <v>55</v>
+        <v>9900</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="92">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Best Workout Clothes for Women: Cost, Lead Times, and MOQs</t>
+          <t>Womens Workout Clothes: How to Choose the Right Partner</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>best workout clothes for women</t>
+          <t>womens workout clothes</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H92" s="6" t="n">
-        <v>57</v>
+        <v>4400</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="93">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Activewear Apparel Brands: A Clear Explainer for Founders</t>
+          <t>Best Workout Clothes for Women: Cost, Lead Times, and MOQs</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>activewear apparel brands</t>
+          <t>best workout clothes for women</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4035,19 +4035,19 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>9900</v>
-      </c>
-      <c r="H93" s="6" t="n">
-        <v>55</v>
+        <v>3600</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="94">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sportswear Articles: Explained in Plain English</t>
+          <t>Men Workout Clothes: How to Choose the Right Partner</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sportswear articles</t>
+          <t>men workout clothes</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4073,19 +4073,19 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>4400</v>
+        <v>2400</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95">
@@ -4096,34 +4096,34 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Company Swag Store: What Established Brands Expect</t>
+          <t>Sportswear Articles: A Founder's Primer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>company swag store</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Custom Merch</t>
+          <t>sportswear articles</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Activewear</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H95" s="4" t="n">
-        <v>25</v>
+        <v>4400</v>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="96">
@@ -4134,34 +4134,34 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Company Swag: A Guide for Brands With Real Budgets</t>
+          <t>What Is a Sportswear: The Short Version for Busy Founders</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>company swag</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Custom Merch</t>
+          <t>what is a sportswear</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Activewear</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="H96" s="5" t="n">
-        <v>43</v>
+      <c r="H96" s="6" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="97">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Company Merch: How to Run a Program That Scales</t>
+          <t>Company Swag Store: What Established Brands Expect</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>company merch</t>
+          <t>company swag store</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>880</v>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>50</v>
+        <v>320</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="98">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Merchandise Maker: A Buyer's Checklist for Brand Teams</t>
+          <t>Company Apparel: What Established Brands Expect</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>merchandise maker</t>
+          <t>company apparel</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>590</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>48</v>
+        <v>880</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="99">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Screen Printing Companies: For Corporate and Hospitality Programs</t>
+          <t>Company Merchandise: From Concept to Delivered Boxes</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>screen printing companies</t>
+          <t>company merchandise</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Company Branded Clothing: From Concept to Delivered Boxes</t>
+          <t>Embroidery Company: A Guide for Brands With Real Budgets</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>company branded clothing</t>
+          <t>embroidery company</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>260</v>
+        <v>590</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Embroidered Sweatshirt: Cost, Minimums, and Lead Times</t>
+          <t>Company Branded Apparel: A Sourcing Guide for Premium Programs</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>embroidered sweatshirt</t>
+          <t>company branded apparel</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>5400</v>
-      </c>
-      <c r="H101" s="4" t="n">
-        <v>17</v>
+        <v>320</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="102">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Corporate Gift Ideas: Ideas That Actually Land</t>
+          <t>Luxury Corporate Gifts: How to Compare Your Options</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>corporate gift ideas</t>
+          <t>luxury corporate gifts</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>3600</v>
+        <v>1000</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Company Swag Ideas: A Brand's Guide to Getting It Right</t>
+          <t>Company Swag Ideas: Ideas That Actually Land</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Embroidered Hoodie: A Quick, Honest Overview</t>
+          <t>Unique Swag Ideas: What Every Marketing Lead Should Know</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>embroidered hoodie</t>
+          <t>unique swag ideas</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -4458,14 +4458,14 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>3600</v>
+        <v>320</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Corporate Apparel: Cost, Minimums, and Lead Times</t>
+          <t>Swag Ideas for Events: What Every Marketing Lead Should Know</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>corporate apparel</t>
+          <t>swag ideas for events</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>4400</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>49</v>
+        <v>260</v>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="106">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Screen Printed Shirts: Premium vs Cheap, Weighed Honestly</t>
+          <t>Screen Printing vs Embroidery vs DTF: Which Is Right for Your Merch</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>screen printed shirts</t>
+          <t>screen printing vs embroidery</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>2900</v>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>31</v>
+        <v>1000</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="107">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Branded Merchandise: Where Most Brands Get It Wrong</t>
+          <t>Corporate Apparel: Premium vs Cheap, Weighed Honestly</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>branded merchandise</t>
+          <t>corporate apparel</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>2400</v>
+        <v>4400</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108">
@@ -4590,12 +4590,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Corporate Gifts: Ideas That Actually Land</t>
+          <t>Branded Merchandise: Premium vs Cheap, Weighed Honestly</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>corporate gifts</t>
+          <t>branded merchandise</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -4605,19 +4605,19 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>6600</v>
+        <v>2400</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="109">
@@ -4628,22 +4628,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Custom Clothing Manufacturers: A Practical Buyer's Guide</t>
+          <t>Custom Swag: How to Choose the Right Partner</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>custom clothing manufacturers</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t>Premium Basics</t>
+          <t>custom swag</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Custom Merch</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4654,8 +4654,8 @@
       <c r="G109" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="H109" s="4" t="n">
-        <v>24</v>
+      <c r="H109" s="5" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="110">
@@ -4666,34 +4666,34 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Clothing Manufacturers Suppliers: A Guide for Established Brands</t>
+          <t>What Is DTG Printing: What You Should Know First</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>clothing manufacturers suppliers</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t>Premium Basics</t>
+          <t>what is dtg printing</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Custom Merch</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>8100</v>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>34</v>
+        <v>1300</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="111">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Custom Hoodie Maker: The Process, Start to Finish</t>
+          <t>Custom Clothing Manufacturers: A Practical Buyer's Guide</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>custom hoodie maker</t>
+          <t>custom clothing manufacturers</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>2900</v>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>34</v>
+        <v>1600</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="112">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>What to Look For in a Body Care Manufacturer</t>
+          <t>Hoodie Maker: What to Expect From a Full-Package Partner</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>body care manufacturers</t>
+          <t>hoodie maker</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>43</v>
+        <v>4400</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="113">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>American Garment Brand: A Production-Partner Checklist</t>
+          <t>Wholesale Clothing Sweatshirts: What Funded Brands Should Look For</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>american garment brand</t>
+          <t>wholesale clothing sweatshirts</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Apparel Manufacturer in USA: What Funded Brands Should Look For</t>
+          <t>Hoodie in Wholesale: From Tech Pack to Delivery</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>apparel manufacturer in usa</t>
+          <t>hoodie in wholesale</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
@@ -4844,8 +4844,8 @@
       <c r="G114" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="H114" s="5" t="n">
-        <v>48</v>
+      <c r="H114" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="115">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Natural Fiber Clothing: How to Compare Your Options</t>
+          <t>American Garment Manufacturers: What to Expect From a Full-Package Partner</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>natural fiber clothing</t>
+          <t>american garment manufacturers</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H115" s="4" t="n">
-        <v>25</v>
+        <v>1600</v>
+      </c>
+      <c r="H115" s="6" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="116">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Custom Sweatshirts: A Side-by-Side Breakdown</t>
+          <t>Clothing Manufacturers in USA: The Process, Start to Finish</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>custom sweatshirts</t>
+          <t>clothing manufacturers in usa</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>12100</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>37</v>
+        <v>1600</v>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="117">
@@ -4932,12 +4932,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Custom Apparel: A Side-by-Side Breakdown</t>
+          <t>Oversized Streetwear Hoodie: A 2026 Buyer's Guide</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>custom apparel</t>
+          <t>oversized streetwear hoodie</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
@@ -4952,14 +4952,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>12100</v>
-      </c>
-      <c r="H117" s="6" t="n">
-        <v>51</v>
+        <v>3600</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="118">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sustainable Clothing: A 2026 Buyer's Guide</t>
+          <t>Full-Package vs Cut-and-Sew: Which Manufacturing Model Fits Your Brand</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>sustainable clothing</t>
+          <t>full package vs cut and sew</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>8100</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>46</v>
+        <v>150</v>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="119">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Clothing Brands: What Every Brand Owner Should Know</t>
+          <t>Streetwear Hoodies: Full-Package vs Cut-and-Sew, Weighed</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>clothing brands</t>
+          <t>streetwear hoodies</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -5023,19 +5023,19 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>27100</v>
+        <v>9900</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Garments Brands, Explained</t>
+          <t>Black Tee: What to Ask Before You Commit</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>garments brands</t>
+          <t>black tee</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -5061,19 +5061,19 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>9900</v>
+        <v>5400</v>
       </c>
       <c r="H120" s="6" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="121">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sustainable Garments: Explained in Plain English</t>
+          <t>American Made Clothing: What Every Brand Owner Should Know</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>sustainable garments</t>
+          <t>american made clothing</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>5400</v>
+        <v>6600</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -5198,7 +5198,7 @@
       <c r="E2" s="3" t="n">
         <v>27100</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="5" t="n">
         <v>83</v>
       </c>
       <c r="G2" s="9" t="inlineStr">
@@ -5231,7 +5231,7 @@
       <c r="E3" s="3" t="n">
         <v>27100</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="5" t="n">
         <v>81</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -5264,7 +5264,7 @@
       <c r="E4" s="3" t="n">
         <v>22200</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -5297,12 +5297,12 @@
       <c r="E5" s="3" t="n">
         <v>22200</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       <c r="E6" s="3" t="n">
         <v>18100</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -5363,12 +5363,12 @@
       <c r="E7" s="3" t="n">
         <v>14800</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       <c r="E8" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
         <v>77</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -5429,7 +5429,7 @@
       <c r="E9" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="n">
         <v>60</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -5462,7 +5462,7 @@
       <c r="E10" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="5" t="n">
         <v>51</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -5495,7 +5495,7 @@
       <c r="E11" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -5528,7 +5528,7 @@
       <c r="E12" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="5" t="n">
         <v>60</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -5561,7 +5561,7 @@
       <c r="E13" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="5" t="n">
         <v>58</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -5594,7 +5594,7 @@
       <c r="E14" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -5627,7 +5627,7 @@
       <c r="E15" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="5" t="n">
         <v>69</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -5660,7 +5660,7 @@
       <c r="E16" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -5693,7 +5693,7 @@
       <c r="E17" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="5" t="n">
         <v>55</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -5726,7 +5726,7 @@
       <c r="E18" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="5" t="n">
         <v>62</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -5792,7 +5792,7 @@
       <c r="E20" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -5825,7 +5825,7 @@
       <c r="E21" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="5" t="n">
         <v>69</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -5858,7 +5858,7 @@
       <c r="E22" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="5" t="n">
         <v>72</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -5891,12 +5891,12 @@
       <c r="E23" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       <c r="E24" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -5957,7 +5957,7 @@
       <c r="E25" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -5990,7 +5990,7 @@
       <c r="E26" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -6023,7 +6023,7 @@
       <c r="E27" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="5" t="n">
         <v>82</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -6056,12 +6056,12 @@
       <c r="E28" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       <c r="E29" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -6122,12 +6122,12 @@
       <c r="E30" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
       <c r="E31" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="5" t="n">
         <v>59</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -6188,12 +6188,12 @@
       <c r="E32" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       <c r="E33" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -6257,9 +6257,9 @@
       <c r="F34" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       <c r="E35" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="5" t="n">
         <v>75</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -6320,7 +6320,7 @@
       <c r="E36" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="5" t="n">
         <v>63</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -6353,7 +6353,7 @@
       <c r="E37" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="5" t="n">
         <v>55</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -6386,7 +6386,7 @@
       <c r="E38" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="5" t="n">
         <v>57</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -6419,7 +6419,7 @@
       <c r="E39" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -6452,7 +6452,7 @@
       <c r="E40" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="5" t="n">
         <v>52</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -6485,7 +6485,7 @@
       <c r="E41" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -6518,7 +6518,7 @@
       <c r="E42" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="5" t="n">
         <v>56</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -6551,7 +6551,7 @@
       <c r="E43" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -6584,7 +6584,7 @@
       <c r="E44" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="5" t="n">
         <v>55</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -6617,7 +6617,7 @@
       <c r="E45" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="5" t="n">
         <v>76</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6650,12 +6650,12 @@
       <c r="E46" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6683,7 @@
       <c r="E47" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6749,7 +6749,7 @@
       <c r="E49" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -6782,7 +6782,7 @@
       <c r="E50" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="5" t="n">
         <v>67</v>
       </c>
       <c r="G50" t="inlineStr">
@@ -6818,9 +6818,9 @@
       <c r="F51" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       <c r="E54" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F54" s="5" t="n">
         <v>56</v>
       </c>
       <c r="G54" t="inlineStr">
@@ -6947,12 +6947,12 @@
       <c r="E55" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F55" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       <c r="E56" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F56" s="5" t="n">
         <v>57</v>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -7013,7 +7013,7 @@
       <c r="E57" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="5" t="n">
         <v>65</v>
       </c>
       <c r="G57" s="9" t="inlineStr">
@@ -7046,7 +7046,7 @@
       <c r="E58" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F58" s="5" t="n">
         <v>61</v>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -7082,9 +7082,9 @@
       <c r="F59" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       <c r="E60" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F60" s="5" t="n">
         <v>74</v>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -7145,7 +7145,7 @@
       <c r="E61" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F61" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -7214,9 +7214,9 @@
       <c r="F63" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7244,12 +7244,12 @@
       <c r="E64" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F64" s="5" t="n">
+      <c r="F64" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       <c r="E65" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="5" t="n">
         <v>54</v>
       </c>
       <c r="G65" t="inlineStr">
@@ -7310,7 +7310,7 @@
       <c r="E66" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F66" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G66" s="9" t="inlineStr">
@@ -7343,7 +7343,7 @@
       <c r="E67" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" s="5" t="n">
         <v>56</v>
       </c>
       <c r="G67" t="inlineStr">
@@ -7376,12 +7376,12 @@
       <c r="E68" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F68" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
       <c r="E69" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F69" s="5" t="n">
         <v>73</v>
       </c>
       <c r="G69" t="inlineStr">
@@ -7475,7 +7475,7 @@
       <c r="E71" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F71" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G71" t="inlineStr">
@@ -7508,12 +7508,12 @@
       <c r="E72" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       <c r="E74" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F74" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G74" s="9" t="inlineStr">
@@ -7640,12 +7640,12 @@
       <c r="E76" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       <c r="E78" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F78" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G78" t="inlineStr">
@@ -7739,7 +7739,7 @@
       <c r="E79" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F79" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G79" t="inlineStr">
@@ -7772,7 +7772,7 @@
       <c r="E80" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="6" t="n">
         <v>45</v>
       </c>
       <c r="G80" t="inlineStr">
@@ -7805,7 +7805,7 @@
       <c r="E81" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="F81" s="5" t="n">
         <v>72</v>
       </c>
       <c r="G81" t="inlineStr">
@@ -7838,7 +7838,7 @@
       <c r="E82" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F82" s="6" t="n">
+      <c r="F82" s="5" t="n">
         <v>51</v>
       </c>
       <c r="G82" t="inlineStr">
@@ -7871,7 +7871,7 @@
       <c r="E83" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F83" s="5" t="n">
+      <c r="F83" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G83" t="inlineStr">
@@ -7904,7 +7904,7 @@
       <c r="E84" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F84" s="5" t="n">
+      <c r="F84" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G84" t="inlineStr">
@@ -7937,7 +7937,7 @@
       <c r="E85" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F85" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G85" s="9" t="inlineStr">
@@ -8003,7 +8003,7 @@
       <c r="E87" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="F87" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G87" t="inlineStr">
@@ -8036,7 +8036,7 @@
       <c r="E88" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F88" s="6" t="n">
+      <c r="F88" s="5" t="n">
         <v>58</v>
       </c>
       <c r="G88" t="inlineStr">
@@ -8069,7 +8069,7 @@
       <c r="E89" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F89" s="5" t="n">
+      <c r="F89" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G89" s="9" t="inlineStr">
@@ -8105,9 +8105,9 @@
       <c r="F90" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8138,9 +8138,9 @@
       <c r="F91" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8168,12 +8168,12 @@
       <c r="E92" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F92" s="5" t="n">
+      <c r="F92" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       <c r="E93" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F93" s="5" t="n">
+      <c r="F93" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G93" s="9" t="inlineStr">
@@ -8234,12 +8234,12 @@
       <c r="E94" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F94" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       <c r="E95" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F95" s="6" t="n">
+      <c r="F95" s="5" t="n">
         <v>78</v>
       </c>
       <c r="G95" t="inlineStr">
@@ -8300,7 +8300,7 @@
       <c r="E96" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F96" s="5" t="n">
+      <c r="F96" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G96" t="inlineStr">
@@ -8333,7 +8333,7 @@
       <c r="E97" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F97" s="6" t="n">
+      <c r="F97" s="5" t="n">
         <v>53</v>
       </c>
       <c r="G97" t="inlineStr">
@@ -8366,7 +8366,7 @@
       <c r="E98" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F98" s="6" t="n">
+      <c r="F98" s="5" t="n">
         <v>64</v>
       </c>
       <c r="G98" t="inlineStr">
@@ -8399,7 +8399,7 @@
       <c r="E99" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F99" s="5" t="n">
+      <c r="F99" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G99" t="inlineStr">
@@ -8432,7 +8432,7 @@
       <c r="E100" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F100" s="6" t="n">
+      <c r="F100" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G100" t="inlineStr">
@@ -8498,7 +8498,7 @@
       <c r="E102" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F102" s="5" t="n">
+      <c r="F102" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G102" t="inlineStr">
@@ -8564,12 +8564,12 @@
       <c r="E104" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F104" s="5" t="n">
+      <c r="F104" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       <c r="E105" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F105" s="6" t="n">
+      <c r="F105" s="5" t="n">
         <v>56</v>
       </c>
       <c r="G105" s="9" t="inlineStr">
@@ -8630,7 +8630,7 @@
       <c r="E106" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F106" s="5" t="n">
+      <c r="F106" s="6" t="n">
         <v>47</v>
       </c>
       <c r="G106" s="9" t="inlineStr">
@@ -8696,7 +8696,7 @@
       <c r="E108" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F108" s="6" t="n">
+      <c r="F108" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G108" t="inlineStr">
@@ -8729,7 +8729,7 @@
       <c r="E109" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F109" s="5" t="n">
+      <c r="F109" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G109" t="inlineStr">
@@ -8762,7 +8762,7 @@
       <c r="E110" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F110" s="6" t="n">
+      <c r="F110" s="5" t="n">
         <v>56</v>
       </c>
       <c r="G110" s="9" t="inlineStr">
@@ -8795,7 +8795,7 @@
       <c r="E111" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F111" s="5" t="n">
+      <c r="F111" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G111" t="inlineStr">
@@ -8828,7 +8828,7 @@
       <c r="E112" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F112" s="6" t="n">
+      <c r="F112" s="5" t="n">
         <v>53</v>
       </c>
       <c r="G112" t="inlineStr">
@@ -8861,7 +8861,7 @@
       <c r="E113" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F113" s="6" t="n">
+      <c r="F113" s="5" t="n">
         <v>81</v>
       </c>
       <c r="G113" t="inlineStr">
@@ -8894,7 +8894,7 @@
       <c r="E114" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F114" s="5" t="n">
+      <c r="F114" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G114" t="inlineStr">
@@ -9059,7 +9059,7 @@
       <c r="E119" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F119" s="6" t="n">
+      <c r="F119" s="5" t="n">
         <v>77</v>
       </c>
       <c r="G119" t="inlineStr">
@@ -9125,12 +9125,12 @@
       <c r="E121" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F121" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       <c r="E122" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F122" s="5" t="n">
+      <c r="F122" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       <c r="E123" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F123" s="5" t="n">
+      <c r="F123" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G123" t="inlineStr">
@@ -9257,7 +9257,7 @@
       <c r="E125" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F125" s="6" t="n">
+      <c r="F125" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G125" t="inlineStr">
@@ -9290,7 +9290,7 @@
       <c r="E126" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F126" s="6" t="n">
+      <c r="F126" s="5" t="n">
         <v>74</v>
       </c>
       <c r="G126" t="inlineStr">
@@ -9323,7 +9323,7 @@
       <c r="E127" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F127" s="6" t="n">
+      <c r="F127" s="5" t="n">
         <v>60</v>
       </c>
       <c r="G127" t="inlineStr">
@@ -9389,7 +9389,7 @@
       <c r="E129" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F129" s="5" t="n">
+      <c r="F129" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G129" t="inlineStr">
@@ -9422,7 +9422,7 @@
       <c r="E130" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F130" s="6" t="n">
+      <c r="F130" s="5" t="n">
         <v>59</v>
       </c>
       <c r="G130" t="inlineStr">
@@ -9455,7 +9455,7 @@
       <c r="E131" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F131" s="5" t="n">
+      <c r="F131" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G131" t="inlineStr">
@@ -9488,7 +9488,7 @@
       <c r="E132" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F132" s="6" t="n">
+      <c r="F132" s="5" t="n">
         <v>70</v>
       </c>
       <c r="G132" t="inlineStr">
@@ -9521,7 +9521,7 @@
       <c r="E133" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F133" s="5" t="n">
+      <c r="F133" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G133" s="9" t="inlineStr">
@@ -9554,7 +9554,7 @@
       <c r="E134" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F134" s="6" t="n">
+      <c r="F134" s="5" t="n">
         <v>58</v>
       </c>
       <c r="G134" t="inlineStr">
@@ -9653,7 +9653,7 @@
       <c r="E137" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F137" s="6" t="n">
+      <c r="F137" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G137" t="inlineStr">
@@ -9752,7 +9752,7 @@
       <c r="E140" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F140" s="5" t="n">
+      <c r="F140" s="6" t="n">
         <v>47</v>
       </c>
       <c r="G140" t="inlineStr">
@@ -9818,7 +9818,7 @@
       <c r="E142" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F142" s="6" t="n">
+      <c r="F142" s="5" t="n">
         <v>59</v>
       </c>
       <c r="G142" t="inlineStr">
@@ -9851,7 +9851,7 @@
       <c r="E143" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F143" s="5" t="n">
+      <c r="F143" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G143" s="9" t="inlineStr">
@@ -9884,7 +9884,7 @@
       <c r="E144" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F144" s="5" t="n">
+      <c r="F144" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G144" s="9" t="inlineStr">
@@ -10016,7 +10016,7 @@
       <c r="E148" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F148" s="5" t="n">
+      <c r="F148" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G148" t="inlineStr">
@@ -10049,7 +10049,7 @@
       <c r="E149" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F149" s="5" t="n">
+      <c r="F149" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G149" t="inlineStr">
@@ -10082,7 +10082,7 @@
       <c r="E150" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F150" s="6" t="n">
+      <c r="F150" s="5" t="n">
         <v>100</v>
       </c>
       <c r="G150" t="inlineStr">
@@ -10115,7 +10115,7 @@
       <c r="E151" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F151" s="5" t="n">
+      <c r="F151" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G151" t="inlineStr">
@@ -10148,12 +10148,12 @@
       <c r="E152" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F152" s="5" t="n">
+      <c r="F152" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       <c r="E153" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F153" s="6" t="n">
+      <c r="F153" s="5" t="n">
         <v>54</v>
       </c>
       <c r="G153" t="inlineStr">
@@ -10214,7 +10214,7 @@
       <c r="E154" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F154" s="5" t="n">
+      <c r="F154" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G154" s="9" t="inlineStr">
@@ -10247,7 +10247,7 @@
       <c r="E155" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F155" s="5" t="n">
+      <c r="F155" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G155" t="inlineStr">
@@ -10280,7 +10280,7 @@
       <c r="E156" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F156" s="6" t="n">
+      <c r="F156" s="5" t="n">
         <v>71</v>
       </c>
       <c r="G156" t="inlineStr">
@@ -10313,7 +10313,7 @@
       <c r="E157" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F157" s="6" t="n">
+      <c r="F157" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G157" t="inlineStr">
@@ -10346,7 +10346,7 @@
       <c r="E158" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F158" s="5" t="n">
+      <c r="F158" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G158" t="inlineStr">
@@ -10379,7 +10379,7 @@
       <c r="E159" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F159" s="6" t="n">
+      <c r="F159" s="5" t="n">
         <v>56</v>
       </c>
       <c r="G159" t="inlineStr">
@@ -10412,7 +10412,7 @@
       <c r="E160" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F160" s="6" t="n">
+      <c r="F160" s="5" t="n">
         <v>89</v>
       </c>
       <c r="G160" t="inlineStr">
@@ -10445,7 +10445,7 @@
       <c r="E161" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F161" s="5" t="n">
+      <c r="F161" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G161" s="9" t="inlineStr">
@@ -10478,7 +10478,7 @@
       <c r="E162" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F162" s="5" t="n">
+      <c r="F162" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G162" t="inlineStr">
@@ -10511,7 +10511,7 @@
       <c r="E163" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F163" s="5" t="n">
+      <c r="F163" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G163" t="inlineStr">
@@ -10544,7 +10544,7 @@
       <c r="E164" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F164" s="5" t="n">
+      <c r="F164" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G164" t="inlineStr">
@@ -10577,7 +10577,7 @@
       <c r="E165" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F165" s="6" t="n">
+      <c r="F165" s="5" t="n">
         <v>63</v>
       </c>
       <c r="G165" t="inlineStr">
@@ -10610,7 +10610,7 @@
       <c r="E166" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F166" s="5" t="n">
+      <c r="F166" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G166" t="inlineStr">
@@ -10643,7 +10643,7 @@
       <c r="E167" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F167" s="5" t="n">
+      <c r="F167" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G167" s="9" t="inlineStr">
@@ -10742,7 +10742,7 @@
       <c r="E170" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F170" s="5" t="n">
+      <c r="F170" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G170" s="9" t="inlineStr">
@@ -10808,7 +10808,7 @@
       <c r="E172" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F172" s="6" t="n">
+      <c r="F172" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G172" t="inlineStr">
@@ -10841,12 +10841,12 @@
       <c r="E173" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F173" s="6" t="n">
+      <c r="F173" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       <c r="E174" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F174" s="6" t="n">
+      <c r="F174" s="5" t="n">
         <v>58</v>
       </c>
       <c r="G174" t="inlineStr">
@@ -10907,7 +10907,7 @@
       <c r="E175" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F175" s="5" t="n">
+      <c r="F175" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G175" t="inlineStr">
@@ -10940,7 +10940,7 @@
       <c r="E176" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F176" s="5" t="n">
+      <c r="F176" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G176" t="inlineStr">
@@ -10973,7 +10973,7 @@
       <c r="E177" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F177" s="5" t="n">
+      <c r="F177" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G177" t="inlineStr">
@@ -11006,7 +11006,7 @@
       <c r="E178" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F178" s="5" t="n">
+      <c r="F178" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G178" t="inlineStr">
@@ -11072,7 +11072,7 @@
       <c r="E180" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F180" s="5" t="n">
+      <c r="F180" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G180" t="inlineStr">
@@ -11105,7 +11105,7 @@
       <c r="E181" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F181" s="6" t="n">
+      <c r="F181" s="5" t="n">
         <v>55</v>
       </c>
       <c r="G181" t="inlineStr">
@@ -11138,7 +11138,7 @@
       <c r="E182" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F182" s="6" t="n">
+      <c r="F182" s="5" t="n">
         <v>51</v>
       </c>
       <c r="G182" t="inlineStr">
@@ -11171,7 +11171,7 @@
       <c r="E183" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F183" s="6" t="n">
+      <c r="F183" s="5" t="n">
         <v>64</v>
       </c>
       <c r="G183" t="inlineStr">
@@ -11204,7 +11204,7 @@
       <c r="E184" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F184" s="5" t="n">
+      <c r="F184" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G184" t="inlineStr">
@@ -11270,7 +11270,7 @@
       <c r="E186" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F186" s="5" t="n">
+      <c r="F186" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G186" t="inlineStr">
@@ -11306,9 +11306,9 @@
       <c r="F187" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G187" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       <c r="E188" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F188" s="5" t="n">
+      <c r="F188" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G188" t="inlineStr">
@@ -11435,7 +11435,7 @@
       <c r="E191" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F191" s="5" t="n">
+      <c r="F191" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G191" t="inlineStr">
@@ -11468,7 +11468,7 @@
       <c r="E192" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F192" s="5" t="n">
+      <c r="F192" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G192" t="inlineStr">
@@ -11501,7 +11501,7 @@
       <c r="E193" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F193" s="5" t="n">
+      <c r="F193" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G193" t="inlineStr">
@@ -11534,7 +11534,7 @@
       <c r="E194" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F194" s="5" t="n">
+      <c r="F194" s="6" t="n">
         <v>45</v>
       </c>
       <c r="G194" t="inlineStr">
@@ -11567,7 +11567,7 @@
       <c r="E195" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F195" s="6" t="n">
+      <c r="F195" s="5" t="n">
         <v>55</v>
       </c>
       <c r="G195" t="inlineStr">
@@ -11600,7 +11600,7 @@
       <c r="E196" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F196" s="5" t="n">
+      <c r="F196" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G196" t="inlineStr">
@@ -11633,7 +11633,7 @@
       <c r="E197" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F197" s="5" t="n">
+      <c r="F197" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G197" t="inlineStr">
@@ -11666,7 +11666,7 @@
       <c r="E198" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F198" s="5" t="n">
+      <c r="F198" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G198" t="inlineStr">
@@ -11699,7 +11699,7 @@
       <c r="E199" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F199" s="6" t="n">
+      <c r="F199" s="5" t="n">
         <v>63</v>
       </c>
       <c r="G199" t="inlineStr">
@@ -11732,7 +11732,7 @@
       <c r="E200" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F200" s="6" t="n">
+      <c r="F200" s="5" t="n">
         <v>77</v>
       </c>
       <c r="G200" s="9" t="inlineStr">
@@ -11765,7 +11765,7 @@
       <c r="E201" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F201" s="5" t="n">
+      <c r="F201" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G201" t="inlineStr">
@@ -11831,7 +11831,7 @@
       <c r="E203" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F203" s="5" t="n">
+      <c r="F203" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G203" t="inlineStr">
@@ -11864,7 +11864,7 @@
       <c r="E204" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F204" s="5" t="n">
+      <c r="F204" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G204" t="inlineStr">
@@ -11897,7 +11897,7 @@
       <c r="E205" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F205" s="6" t="n">
+      <c r="F205" s="5" t="n">
         <v>59</v>
       </c>
       <c r="G205" t="inlineStr">
@@ -11963,7 +11963,7 @@
       <c r="E207" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F207" s="6" t="n">
+      <c r="F207" s="5" t="n">
         <v>61</v>
       </c>
       <c r="G207" t="inlineStr">
@@ -11999,9 +11999,9 @@
       <c r="F208" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G208" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       <c r="E209" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F209" s="5" t="n">
+      <c r="F209" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G209" t="inlineStr">
@@ -12128,7 +12128,7 @@
       <c r="E212" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F212" s="6" t="n">
+      <c r="F212" s="5" t="n">
         <v>65</v>
       </c>
       <c r="G212" t="inlineStr">
@@ -12293,7 +12293,7 @@
       <c r="E217" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F217" s="6" t="n">
+      <c r="F217" s="5" t="n">
         <v>61</v>
       </c>
       <c r="G217" t="inlineStr">
@@ -12359,7 +12359,7 @@
       <c r="E219" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F219" s="5" t="n">
+      <c r="F219" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G219" t="inlineStr">
@@ -12425,12 +12425,12 @@
       <c r="E221" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F221" s="5" t="n">
+      <c r="F221" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G221" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12458,7 @@
       <c r="E222" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F222" s="6" t="n">
+      <c r="F222" s="5" t="n">
         <v>74</v>
       </c>
       <c r="G222" t="inlineStr">
@@ -12491,7 +12491,7 @@
       <c r="E223" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F223" s="6" t="n">
+      <c r="F223" s="5" t="n">
         <v>52</v>
       </c>
       <c r="G223" t="inlineStr">
@@ -12524,7 +12524,7 @@
       <c r="E224" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F224" s="5" t="n">
+      <c r="F224" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G224" t="inlineStr">
@@ -12557,7 +12557,7 @@
       <c r="E225" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F225" s="5" t="n">
+      <c r="F225" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G225" t="inlineStr">
@@ -12590,7 +12590,7 @@
       <c r="E226" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F226" s="6" t="n">
+      <c r="F226" s="5" t="n">
         <v>51</v>
       </c>
       <c r="G226" t="inlineStr">
@@ -12623,7 +12623,7 @@
       <c r="E227" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F227" s="5" t="n">
+      <c r="F227" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G227" t="inlineStr">
@@ -12656,7 +12656,7 @@
       <c r="E228" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F228" s="5" t="n">
+      <c r="F228" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G228" t="inlineStr">
@@ -12689,7 +12689,7 @@
       <c r="E229" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F229" s="6" t="n">
+      <c r="F229" s="5" t="n">
         <v>64</v>
       </c>
       <c r="G229" t="inlineStr">
@@ -12755,7 +12755,7 @@
       <c r="E231" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F231" s="5" t="n">
+      <c r="F231" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G231" t="inlineStr">
@@ -12788,7 +12788,7 @@
       <c r="E232" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F232" s="5" t="n">
+      <c r="F232" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G232" t="inlineStr">
@@ -12821,7 +12821,7 @@
       <c r="E233" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F233" s="5" t="n">
+      <c r="F233" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G233" t="inlineStr">
@@ -12854,7 +12854,7 @@
       <c r="E234" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F234" s="5" t="n">
+      <c r="F234" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G234" t="inlineStr">
@@ -12887,7 +12887,7 @@
       <c r="E235" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F235" s="5" t="n">
+      <c r="F235" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G235" t="inlineStr">
@@ -12953,7 +12953,7 @@
       <c r="E237" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F237" s="6" t="n">
+      <c r="F237" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G237" t="inlineStr">
@@ -12986,7 +12986,7 @@
       <c r="E238" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F238" s="5" t="n">
+      <c r="F238" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G238" t="inlineStr">
@@ -13019,7 +13019,7 @@
       <c r="E239" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F239" s="5" t="n">
+      <c r="F239" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G239" t="inlineStr">
@@ -13052,7 +13052,7 @@
       <c r="E240" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F240" s="5" t="n">
+      <c r="F240" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G240" t="inlineStr">
@@ -13085,7 +13085,7 @@
       <c r="E241" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F241" s="5" t="n">
+      <c r="F241" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G241" t="inlineStr">
@@ -13217,7 +13217,7 @@
       <c r="E245" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F245" s="5" t="n">
+      <c r="F245" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G245" t="inlineStr">
@@ -13253,9 +13253,9 @@
       <c r="F246" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G246" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -13283,7 +13283,7 @@
       <c r="E247" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F247" s="6" t="n">
+      <c r="F247" s="5" t="n">
         <v>69</v>
       </c>
       <c r="G247" t="inlineStr">
@@ -13382,7 +13382,7 @@
       <c r="E250" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F250" s="6" t="n">
+      <c r="F250" s="5" t="n">
         <v>60</v>
       </c>
       <c r="G250" t="inlineStr">
@@ -13415,7 +13415,7 @@
       <c r="E251" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F251" s="5" t="n">
+      <c r="F251" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G251" t="inlineStr">
@@ -13448,7 +13448,7 @@
       <c r="E252" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F252" s="6" t="n">
+      <c r="F252" s="5" t="n">
         <v>63</v>
       </c>
       <c r="G252" t="inlineStr">
@@ -13481,7 +13481,7 @@
       <c r="E253" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F253" s="6" t="n">
+      <c r="F253" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G253" t="inlineStr">
@@ -13514,7 +13514,7 @@
       <c r="E254" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F254" s="5" t="n">
+      <c r="F254" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G254" t="inlineStr">
@@ -13547,7 +13547,7 @@
       <c r="E255" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F255" s="5" t="n">
+      <c r="F255" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G255" t="inlineStr">
@@ -13580,7 +13580,7 @@
       <c r="E256" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F256" s="6" t="n">
+      <c r="F256" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G256" t="inlineStr">
@@ -13613,7 +13613,7 @@
       <c r="E257" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F257" s="6" t="n">
+      <c r="F257" s="5" t="n">
         <v>70</v>
       </c>
       <c r="G257" t="inlineStr">
@@ -13646,7 +13646,7 @@
       <c r="E258" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F258" s="5" t="n">
+      <c r="F258" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G258" t="inlineStr">
@@ -13679,7 +13679,7 @@
       <c r="E259" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F259" s="5" t="n">
+      <c r="F259" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G259" t="inlineStr">
@@ -13712,7 +13712,7 @@
       <c r="E260" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F260" s="5" t="n">
+      <c r="F260" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G260" t="inlineStr">
@@ -13745,7 +13745,7 @@
       <c r="E261" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F261" s="5" t="n">
+      <c r="F261" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G261" t="inlineStr">
@@ -13778,7 +13778,7 @@
       <c r="E262" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F262" s="5" t="n">
+      <c r="F262" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G262" t="inlineStr">
@@ -13844,7 +13844,7 @@
       <c r="E264" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F264" s="6" t="n">
+      <c r="F264" s="5" t="n">
         <v>52</v>
       </c>
       <c r="G264" t="inlineStr">
@@ -13910,7 +13910,7 @@
       <c r="E266" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F266" s="6" t="n">
+      <c r="F266" s="5" t="n">
         <v>54</v>
       </c>
       <c r="G266" t="inlineStr">
@@ -14009,7 +14009,7 @@
       <c r="E269" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F269" s="5" t="n">
+      <c r="F269" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G269" t="inlineStr">
@@ -14042,7 +14042,7 @@
       <c r="E270" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F270" s="5" t="n">
+      <c r="F270" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G270" t="inlineStr">
@@ -14108,7 +14108,7 @@
       <c r="E272" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F272" s="6" t="n">
+      <c r="F272" s="5" t="n">
         <v>53</v>
       </c>
       <c r="G272" t="inlineStr">
@@ -14207,7 +14207,7 @@
       <c r="E275" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F275" s="6" t="n">
+      <c r="F275" s="5" t="n">
         <v>77</v>
       </c>
       <c r="G275" s="9" t="inlineStr">
@@ -14273,7 +14273,7 @@
       <c r="E277" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F277" s="6" t="n">
+      <c r="F277" s="5" t="n">
         <v>70</v>
       </c>
       <c r="G277" t="inlineStr">
@@ -14306,7 +14306,7 @@
       <c r="E278" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F278" s="5" t="n">
+      <c r="F278" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G278" t="inlineStr">
@@ -14339,7 +14339,7 @@
       <c r="E279" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F279" s="5" t="n">
+      <c r="F279" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G279" t="inlineStr">
@@ -14375,9 +14375,9 @@
       <c r="F280" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G280" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       <c r="E281" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F281" s="6" t="n">
+      <c r="F281" s="5" t="n">
         <v>79</v>
       </c>
       <c r="G281" t="inlineStr">
@@ -14438,7 +14438,7 @@
       <c r="E282" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F282" s="6" t="n">
+      <c r="F282" s="5" t="n">
         <v>74</v>
       </c>
       <c r="G282" t="inlineStr">
@@ -14504,7 +14504,7 @@
       <c r="E284" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F284" s="6" t="n">
+      <c r="F284" s="5" t="n">
         <v>58</v>
       </c>
       <c r="G284" t="inlineStr">
@@ -14570,7 +14570,7 @@
       <c r="E286" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F286" s="5" t="n">
+      <c r="F286" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G286" t="inlineStr">
@@ -14603,7 +14603,7 @@
       <c r="E287" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F287" s="5" t="n">
+      <c r="F287" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G287" t="inlineStr">
@@ -14636,7 +14636,7 @@
       <c r="E288" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F288" s="5" t="n">
+      <c r="F288" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G288" t="inlineStr">
@@ -14768,7 +14768,7 @@
       <c r="E292" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F292" s="5" t="n">
+      <c r="F292" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G292" t="inlineStr">
@@ -14801,7 +14801,7 @@
       <c r="E293" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F293" s="5" t="n">
+      <c r="F293" s="6" t="n">
         <v>45</v>
       </c>
       <c r="G293" t="inlineStr">
@@ -14867,7 +14867,7 @@
       <c r="E295" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F295" s="5" t="n">
+      <c r="F295" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G295" t="inlineStr">
@@ -14933,7 +14933,7 @@
       <c r="E297" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F297" s="5" t="n">
+      <c r="F297" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G297" s="9" t="inlineStr">
@@ -14966,7 +14966,7 @@
       <c r="E298" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F298" s="6" t="n">
+      <c r="F298" s="5" t="n">
         <v>51</v>
       </c>
       <c r="G298" s="9" t="inlineStr">
@@ -15032,7 +15032,7 @@
       <c r="E300" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F300" s="5" t="n">
+      <c r="F300" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G300" t="inlineStr">
@@ -15065,7 +15065,7 @@
       <c r="E301" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F301" s="5" t="n">
+      <c r="F301" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G301" t="inlineStr">
@@ -15197,7 +15197,7 @@
       <c r="E305" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F305" s="6" t="n">
+      <c r="F305" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G305" t="inlineStr">
@@ -15230,7 +15230,7 @@
       <c r="E306" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F306" s="5" t="n">
+      <c r="F306" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G306" t="inlineStr">
@@ -15263,7 +15263,7 @@
       <c r="E307" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F307" s="5" t="n">
+      <c r="F307" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G307" t="inlineStr">
@@ -15362,7 +15362,7 @@
       <c r="E310" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F310" s="5" t="n">
+      <c r="F310" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G310" t="inlineStr">
@@ -15395,7 +15395,7 @@
       <c r="E311" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F311" s="5" t="n">
+      <c r="F311" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G311" t="inlineStr">
@@ -15461,7 +15461,7 @@
       <c r="E313" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F313" s="5" t="n">
+      <c r="F313" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G313" t="inlineStr">
@@ -15494,7 +15494,7 @@
       <c r="E314" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F314" s="5" t="n">
+      <c r="F314" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G314" t="inlineStr">
@@ -15527,7 +15527,7 @@
       <c r="E315" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F315" s="6" t="n">
+      <c r="F315" s="5" t="n">
         <v>58</v>
       </c>
       <c r="G315" t="inlineStr">
@@ -15560,7 +15560,7 @@
       <c r="E316" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F316" s="5" t="n">
+      <c r="F316" s="6" t="n">
         <v>47</v>
       </c>
       <c r="G316" t="inlineStr">
@@ -15593,7 +15593,7 @@
       <c r="E317" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F317" s="5" t="n">
+      <c r="F317" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G317" t="inlineStr">
@@ -15626,7 +15626,7 @@
       <c r="E318" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F318" s="6" t="n">
+      <c r="F318" s="5" t="n">
         <v>55</v>
       </c>
       <c r="G318" t="inlineStr">
@@ -15659,7 +15659,7 @@
       <c r="E319" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F319" s="5" t="n">
+      <c r="F319" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G319" t="inlineStr">
@@ -15692,7 +15692,7 @@
       <c r="E320" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F320" s="6" t="n">
+      <c r="F320" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G320" s="9" t="inlineStr">
@@ -15725,7 +15725,7 @@
       <c r="E321" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F321" s="5" t="n">
+      <c r="F321" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G321" t="inlineStr">
@@ -15758,7 +15758,7 @@
       <c r="E322" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F322" s="6" t="n">
+      <c r="F322" s="5" t="n">
         <v>54</v>
       </c>
       <c r="G322" t="inlineStr">
@@ -15824,7 +15824,7 @@
       <c r="E324" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F324" s="5" t="n">
+      <c r="F324" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G324" s="9" t="inlineStr">
@@ -15890,7 +15890,7 @@
       <c r="E326" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F326" s="5" t="n">
+      <c r="F326" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G326" t="inlineStr">
@@ -15956,7 +15956,7 @@
       <c r="E328" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F328" s="6" t="n">
+      <c r="F328" s="5" t="n">
         <v>58</v>
       </c>
       <c r="G328" t="inlineStr">
@@ -15989,7 +15989,7 @@
       <c r="E329" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F329" s="5" t="n">
+      <c r="F329" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G329" t="inlineStr">
@@ -16025,9 +16025,9 @@
       <c r="F330" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G330" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -16088,7 +16088,7 @@
       <c r="E332" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F332" s="5" t="n">
+      <c r="F332" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G332" t="inlineStr">
@@ -16154,7 +16154,7 @@
       <c r="E334" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F334" s="5" t="n">
+      <c r="F334" s="6" t="n">
         <v>45</v>
       </c>
       <c r="G334" t="inlineStr">
@@ -16187,7 +16187,7 @@
       <c r="E335" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F335" s="5" t="n">
+      <c r="F335" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G335" t="inlineStr">
@@ -16220,7 +16220,7 @@
       <c r="E336" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F336" s="5" t="n">
+      <c r="F336" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G336" t="inlineStr">
@@ -16253,7 +16253,7 @@
       <c r="E337" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F337" s="5" t="n">
+      <c r="F337" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G337" t="inlineStr">
@@ -16286,7 +16286,7 @@
       <c r="E338" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F338" s="5" t="n">
+      <c r="F338" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G338" t="inlineStr">
@@ -16319,7 +16319,7 @@
       <c r="E339" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F339" s="5" t="n">
+      <c r="F339" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G339" t="inlineStr">
@@ -16385,7 +16385,7 @@
       <c r="E341" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F341" s="5" t="n">
+      <c r="F341" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G341" t="inlineStr">
@@ -16418,7 +16418,7 @@
       <c r="E342" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F342" s="5" t="n">
+      <c r="F342" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G342" t="inlineStr">
@@ -16484,7 +16484,7 @@
       <c r="E344" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F344" s="5" t="n">
+      <c r="F344" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G344" t="inlineStr">
@@ -16550,7 +16550,7 @@
       <c r="E346" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F346" s="6" t="n">
+      <c r="F346" s="5" t="n">
         <v>100</v>
       </c>
       <c r="G346" t="inlineStr">
@@ -16583,7 +16583,7 @@
       <c r="E347" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F347" s="5" t="n">
+      <c r="F347" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G347" t="inlineStr">
@@ -16616,7 +16616,7 @@
       <c r="E348" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F348" s="5" t="n">
+      <c r="F348" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G348" t="inlineStr">
@@ -16682,7 +16682,7 @@
       <c r="E350" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F350" s="5" t="n">
+      <c r="F350" s="6" t="n">
         <v>47</v>
       </c>
       <c r="G350" t="inlineStr">
@@ -16748,7 +16748,7 @@
       <c r="E352" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F352" s="5" t="n">
+      <c r="F352" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G352" t="inlineStr">
@@ -16781,7 +16781,7 @@
       <c r="E353" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F353" s="5" t="n">
+      <c r="F353" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G353" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="E354" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F354" s="5" t="n">
+      <c r="F354" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G354" t="inlineStr">
@@ -16847,7 +16847,7 @@
       <c r="E355" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F355" s="6" t="n">
+      <c r="F355" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G355" t="inlineStr">
@@ -16946,7 +16946,7 @@
       <c r="E358" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F358" s="6" t="n">
+      <c r="F358" s="5" t="n">
         <v>65</v>
       </c>
       <c r="G358" t="inlineStr">
@@ -17012,7 +17012,7 @@
       <c r="E360" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F360" s="6" t="n">
+      <c r="F360" s="5" t="n">
         <v>65</v>
       </c>
       <c r="G360" t="inlineStr">
@@ -17045,7 +17045,7 @@
       <c r="E361" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F361" s="6" t="n">
+      <c r="F361" s="5" t="n">
         <v>63</v>
       </c>
       <c r="G361" t="inlineStr">
@@ -17078,7 +17078,7 @@
       <c r="E362" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F362" s="5" t="n">
+      <c r="F362" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G362" t="inlineStr">
@@ -17144,7 +17144,7 @@
       <c r="E364" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F364" s="5" t="n">
+      <c r="F364" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G364" t="inlineStr">
@@ -17177,7 +17177,7 @@
       <c r="E365" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F365" s="5" t="n">
+      <c r="F365" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G365" t="inlineStr">
@@ -17210,7 +17210,7 @@
       <c r="E366" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F366" s="5" t="n">
+      <c r="F366" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G366" t="inlineStr">
@@ -17243,7 +17243,7 @@
       <c r="E367" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F367" s="6" t="n">
+      <c r="F367" s="5" t="n">
         <v>82</v>
       </c>
       <c r="G367" t="inlineStr">
@@ -17276,7 +17276,7 @@
       <c r="E368" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F368" s="5" t="n">
+      <c r="F368" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G368" t="inlineStr">
@@ -17309,7 +17309,7 @@
       <c r="E369" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F369" s="5" t="n">
+      <c r="F369" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G369" t="inlineStr">
@@ -17342,7 +17342,7 @@
       <c r="E370" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F370" s="5" t="n">
+      <c r="F370" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G370" t="inlineStr">
@@ -17375,7 +17375,7 @@
       <c r="E371" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F371" s="6" t="n">
+      <c r="F371" s="5" t="n">
         <v>69</v>
       </c>
       <c r="G371" t="inlineStr">
@@ -17441,7 +17441,7 @@
       <c r="E373" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F373" s="5" t="n">
+      <c r="F373" s="6" t="n">
         <v>47</v>
       </c>
       <c r="G373" t="inlineStr">
@@ -17474,7 +17474,7 @@
       <c r="E374" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F374" s="6" t="n">
+      <c r="F374" s="5" t="n">
         <v>100</v>
       </c>
       <c r="G374" t="inlineStr">
@@ -17507,7 +17507,7 @@
       <c r="E375" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F375" s="6" t="n">
+      <c r="F375" s="5" t="n">
         <v>82</v>
       </c>
       <c r="G375" t="inlineStr">
@@ -17540,7 +17540,7 @@
       <c r="E376" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F376" s="6" t="n">
+      <c r="F376" s="5" t="n">
         <v>55</v>
       </c>
       <c r="G376" t="inlineStr">
@@ -17573,7 +17573,7 @@
       <c r="E377" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F377" s="5" t="n">
+      <c r="F377" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G377" t="inlineStr">
@@ -17606,7 +17606,7 @@
       <c r="E378" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F378" s="5" t="n">
+      <c r="F378" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G378" t="inlineStr">
@@ -17672,7 +17672,7 @@
       <c r="E380" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F380" s="6" t="n">
+      <c r="F380" s="5" t="n">
         <v>65</v>
       </c>
       <c r="G380" t="inlineStr">
@@ -17771,7 +17771,7 @@
       <c r="E383" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F383" s="5" t="n">
+      <c r="F383" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G383" t="inlineStr">
@@ -17804,7 +17804,7 @@
       <c r="E384" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F384" s="5" t="n">
+      <c r="F384" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G384" t="inlineStr">
@@ -17870,7 +17870,7 @@
       <c r="E386" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F386" s="5" t="n">
+      <c r="F386" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G386" t="inlineStr">
@@ -17969,7 +17969,7 @@
       <c r="E389" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F389" s="6" t="n">
+      <c r="F389" s="5" t="n">
         <v>68</v>
       </c>
       <c r="G389" s="9" t="inlineStr">
@@ -18101,7 +18101,7 @@
       <c r="E393" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F393" s="6" t="n">
+      <c r="F393" s="5" t="n">
         <v>75</v>
       </c>
       <c r="G393" t="inlineStr">
@@ -18134,7 +18134,7 @@
       <c r="E394" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F394" s="5" t="n">
+      <c r="F394" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G394" t="inlineStr">
@@ -18170,9 +18170,9 @@
       <c r="F395" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G395" s="9" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       <c r="E397" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F397" s="6" t="n">
+      <c r="F397" s="5" t="n">
         <v>57</v>
       </c>
       <c r="G397" t="inlineStr">
@@ -18266,7 +18266,7 @@
       <c r="E398" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F398" s="6" t="n">
+      <c r="F398" s="5" t="n">
         <v>51</v>
       </c>
       <c r="G398" t="inlineStr">
@@ -18299,7 +18299,7 @@
       <c r="E399" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F399" s="6" t="n">
+      <c r="F399" s="5" t="n">
         <v>57</v>
       </c>
       <c r="G399" t="inlineStr">
@@ -18332,7 +18332,7 @@
       <c r="E400" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F400" s="5" t="n">
+      <c r="F400" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G400" t="inlineStr">
@@ -18365,7 +18365,7 @@
       <c r="E401" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F401" s="5" t="n">
+      <c r="F401" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G401" t="inlineStr">
@@ -18398,7 +18398,7 @@
       <c r="E402" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F402" s="5" t="n">
+      <c r="F402" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G402" t="inlineStr">
@@ -18431,7 +18431,7 @@
       <c r="E403" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F403" s="5" t="n">
+      <c r="F403" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G403" t="inlineStr">
@@ -18497,7 +18497,7 @@
       <c r="E405" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F405" s="6" t="n">
+      <c r="F405" s="5" t="n">
         <v>65</v>
       </c>
       <c r="G405" t="inlineStr">
@@ -18530,7 +18530,7 @@
       <c r="E406" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F406" s="5" t="n">
+      <c r="F406" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G406" t="inlineStr">
@@ -18563,7 +18563,7 @@
       <c r="E407" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F407" s="6" t="n">
+      <c r="F407" s="5" t="n">
         <v>60</v>
       </c>
       <c r="G407" t="inlineStr">
@@ -18629,7 +18629,7 @@
       <c r="E409" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F409" s="6" t="n">
+      <c r="F409" s="5" t="n">
         <v>77</v>
       </c>
       <c r="G409" t="inlineStr">
@@ -18695,7 +18695,7 @@
       <c r="E411" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F411" s="5" t="n">
+      <c r="F411" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G411" t="inlineStr">
@@ -18728,7 +18728,7 @@
       <c r="E412" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F412" s="6" t="n">
+      <c r="F412" s="5" t="n">
         <v>70</v>
       </c>
       <c r="G412" t="inlineStr">
@@ -18860,7 +18860,7 @@
       <c r="E416" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F416" s="5" t="n">
+      <c r="F416" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G416" s="9" t="inlineStr">
@@ -18893,7 +18893,7 @@
       <c r="E417" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F417" s="5" t="n">
+      <c r="F417" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G417" t="inlineStr">
@@ -18926,7 +18926,7 @@
       <c r="E418" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F418" s="5" t="n">
+      <c r="F418" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G418" t="inlineStr">
@@ -18992,7 +18992,7 @@
       <c r="E420" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F420" s="5" t="n">
+      <c r="F420" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G420" t="inlineStr">
@@ -19091,7 +19091,7 @@
       <c r="B2" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>44</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -19114,7 +19114,7 @@
       <c r="B3" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>41</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -19137,7 +19137,7 @@
       <c r="B4" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>37</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -19160,7 +19160,7 @@
       <c r="B5" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5" t="n">
         <v>85</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -19183,7 +19183,7 @@
       <c r="B6" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
         <v>83</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -19206,7 +19206,7 @@
       <c r="B7" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="5" t="n">
         <v>88</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -19229,7 +19229,7 @@
       <c r="B8" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -19252,7 +19252,7 @@
       <c r="B9" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>36</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -19298,7 +19298,7 @@
       <c r="B11" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="5" t="n">
         <v>60</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -19321,7 +19321,7 @@
       <c r="B12" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>42</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -19344,7 +19344,7 @@
       <c r="B13" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="5" t="n">
         <v>59</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -19367,7 +19367,7 @@
       <c r="B14" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>36</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -19390,7 +19390,7 @@
       <c r="B15" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>47</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -19413,7 +19413,7 @@
       <c r="B16" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="5" t="n">
         <v>51</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -19436,7 +19436,7 @@
       <c r="B17" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="5" t="n">
         <v>54</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -19459,7 +19459,7 @@
       <c r="B18" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="5" t="n">
         <v>81</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -19482,7 +19482,7 @@
       <c r="B19" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <v>41</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -19505,7 +19505,7 @@
       <c r="B20" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="5" t="n">
         <v>65</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -19528,7 +19528,7 @@
       <c r="B21" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="6" t="n">
         <v>44</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -19574,7 +19574,7 @@
       <c r="B23" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="5" t="n">
         <v>78</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -19597,7 +19597,7 @@
       <c r="B24" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="6" t="n">
         <v>35</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -19666,7 +19666,7 @@
       <c r="B27" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="5" t="n">
         <v>80</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -19689,7 +19689,7 @@
       <c r="B28" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="5" t="n">
         <v>58</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -19712,7 +19712,7 @@
       <c r="B29" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="6" t="n">
         <v>36</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -19735,7 +19735,7 @@
       <c r="B30" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="6" t="n">
         <v>39</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -19781,7 +19781,7 @@
       <c r="B32" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="5" t="n">
         <v>50</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -19804,7 +19804,7 @@
       <c r="B33" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -19827,7 +19827,7 @@
       <c r="B34" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="6" t="n">
         <v>35</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -19850,7 +19850,7 @@
       <c r="B35" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="6" t="n">
         <v>42</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -19873,7 +19873,7 @@
       <c r="B36" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -19896,7 +19896,7 @@
       <c r="B37" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="6" t="n">
         <v>43</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -19919,7 +19919,7 @@
       <c r="B38" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="6" t="n">
         <v>39</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -19942,7 +19942,7 @@
       <c r="B39" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="6" t="n">
         <v>41</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -20057,7 +20057,7 @@
       <c r="B44" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="6" t="n">
         <v>37</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -20080,7 +20080,7 @@
       <c r="B45" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="6" t="n">
         <v>43</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -20103,7 +20103,7 @@
       <c r="B46" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C46" s="5" t="n">
         <v>50</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -20149,7 +20149,7 @@
       <c r="B48" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -20195,7 +20195,7 @@
       <c r="B50" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="6" t="n">
         <v>39</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -20218,7 +20218,7 @@
       <c r="B51" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="6" t="n">
         <v>35</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -20264,7 +20264,7 @@
       <c r="B53" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -20287,7 +20287,7 @@
       <c r="B54" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -20310,7 +20310,7 @@
       <c r="B55" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="6" t="n">
         <v>49</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -20333,7 +20333,7 @@
       <c r="B56" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="C56" s="6" t="n">
+      <c r="C56" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D56" t="inlineStr">
